--- a/excelReport/status-code-report.xlsx
+++ b/excelReport/status-code-report.xlsx
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.softwebsolutions.com/supply-chain/</v>
+        <v>https://www.softwebsolutions.com/digital-transformation-consulting/</v>
       </c>
       <c r="B2">
         <v>200</v>
@@ -423,7 +423,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.softwebsolutions.com/manufacturing-industry/</v>
+        <v>https://www.softwebsolutions.com/business-process-automation-services/</v>
       </c>
       <c r="B3">
         <v>200</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://www.softwebsolutions.com/semiconductor/</v>
+        <v>https://www.softwebsolutions.com/product-engineering-service/</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -445,7 +445,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://www.softwebsolutions.com/telecom-industry/</v>
+        <v>https://www.softwebsolutions.com/enterprise-app-development/</v>
       </c>
       <c r="B5">
         <v>200</v>
@@ -456,7 +456,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://www.softwebsolutions.com/finance-industry/</v>
+        <v>https://www.softwebsolutions.com/custom-software-development/</v>
       </c>
       <c r="B6">
         <v>200</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://www.softwebsolutions.com/portfolio/</v>
+        <v>https://www.softwebsolutions.com/legacy-application-modernization/</v>
       </c>
       <c r="B7">
         <v>200</v>
@@ -478,7 +478,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://www.softwebsolutions.com/about-softweb-solutions/</v>
+        <v>https://www.softwebsolutions.com/devops-consulting-services/</v>
       </c>
       <c r="B8">
         <v>200</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://www.softwebsolutions.com/client-testimonial/</v>
+        <v>https://www.softwebsolutions.com/full-stack-development-company/</v>
       </c>
       <c r="B9">
         <v>200</v>
@@ -500,7 +500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://www.softwebsolutions.com/resources/</v>
+        <v>https://www.softwebsolutions.com/ai-automation-testing-services/</v>
       </c>
       <c r="B10">
         <v>200</v>
@@ -511,7 +511,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://www.softwebsolutions.com/digital-transformation-consulting/</v>
+        <v>https://www.softwebsolutions.com/data-analytics-services/</v>
       </c>
       <c r="B11">
         <v>200</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://www.softwebsolutions.com/business-process-automation-services/</v>
+        <v>https://www.softwebsolutions.com/data-visualization-consulting/</v>
       </c>
       <c r="B12">
         <v>200</v>
@@ -533,7 +533,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://www.softwebsolutions.com/product-engineering-service/</v>
+        <v>https://www.softwebsolutions.com/data-engineering-consulting-services/</v>
       </c>
       <c r="B13">
         <v>200</v>
@@ -544,7 +544,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://www.softwebsolutions.com/enterprise-app-development/</v>
+        <v>https://www.softwebsolutions.com/snowflake-consulting-services/</v>
       </c>
       <c r="B14">
         <v>200</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://www.softwebsolutions.com/custom-software-development/</v>
+        <v>https://www.softwebsolutions.com/data-science-development/</v>
       </c>
       <c r="B15">
         <v>200</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://www.softwebsolutions.com/legacy-application-modernization/</v>
+        <v>https://www.softwebsolutions.com/business-intelligence-consulting/</v>
       </c>
       <c r="B16">
         <v>200</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://www.softwebsolutions.com/devops-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/cloud-consulting-services/</v>
       </c>
       <c r="B17">
         <v>200</v>
@@ -588,7 +588,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://www.softwebsolutions.com/full-stack-development-company/</v>
+        <v>https://www.softwebsolutions.com/cloud-migration-services/</v>
       </c>
       <c r="B18">
         <v>200</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://www.softwebsolutions.com/ai-automation-testing-services/</v>
+        <v>https://www.softwebsolutions.com/multicloud-managed-services/</v>
       </c>
       <c r="B19">
         <v>200</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://www.softwebsolutions.com/data-analytics-services/</v>
+        <v>https://www.softwebsolutions.com/ai-consulting-services/</v>
       </c>
       <c r="B20">
         <v>200</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://www.softwebsolutions.com/data-visualization-consulting/</v>
+        <v>https://www.softwebsolutions.com/agentic-ai-services/</v>
       </c>
       <c r="B21">
         <v>200</v>
@@ -632,7 +632,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://www.softwebsolutions.com/data-engineering-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/edge-ai-solutions/</v>
       </c>
       <c r="B22">
         <v>200</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://www.softwebsolutions.com/snowflake-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/generative-ai-consulting-services/</v>
       </c>
       <c r="B23">
         <v>200</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://www.softwebsolutions.com/data-science-development/</v>
+        <v>https://www.softwebsolutions.com/computer-vision/</v>
       </c>
       <c r="B24">
         <v>200</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://www.softwebsolutions.com/business-intelligence-consulting/</v>
+        <v>https://www.softwebsolutions.com/machine-learning-services/</v>
       </c>
       <c r="B25">
         <v>200</v>
@@ -676,7 +676,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://www.softwebsolutions.com/cloud-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/ai-agent-development-company</v>
       </c>
       <c r="B26">
         <v>200</v>
@@ -687,7 +687,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://www.softwebsolutions.com/cloud-migration-services/</v>
+        <v>https://www.softwebsolutions.com/needle/manufacturing/</v>
       </c>
       <c r="B27">
         <v>200</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://www.softwebsolutions.com/multicloud-managed-services/</v>
+        <v>https://www.softwebsolutions.com/needle/finance/</v>
       </c>
       <c r="B28">
         <v>200</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://www.softwebsolutions.com/ai-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/microsoft-consulting-services/</v>
       </c>
       <c r="B29">
         <v>200</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://www.softwebsolutions.com/agentic-ai-services/</v>
+        <v>https://www.softwebsolutions.com/fabric-consulting-services/</v>
       </c>
       <c r="B30">
         <v>200</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://www.softwebsolutions.com/edge-ai-solutions/</v>
+        <v>https://www.softwebsolutions.com/microsoft-copilot-studio-consulting/</v>
       </c>
       <c r="B31">
         <v>200</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://www.softwebsolutions.com/generative-ai-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/microsoft-365-consulting-services/</v>
       </c>
       <c r="B32">
         <v>200</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://www.softwebsolutions.com/computer-vision/</v>
+        <v>https://www.softwebsolutions.com/net-maui-development-services/</v>
       </c>
       <c r="B33">
         <v>200</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://www.softwebsolutions.com/machine-learning-services/</v>
+        <v>https://www.softwebsolutions.com/power-platform-consulting-services/</v>
       </c>
       <c r="B34">
         <v>200</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://www.softwebsolutions.com/ai-agent-development-company</v>
+        <v>https://www.softwebsolutions.com/microsoft-power-apps-development/</v>
       </c>
       <c r="B35">
         <v>200</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://www.softwebsolutions.com/needle/manufacturing/</v>
+        <v>https://www.softwebsolutions.com/power-automate-consulting/</v>
       </c>
       <c r="B36">
         <v>200</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://www.softwebsolutions.com/needle/finance/</v>
+        <v>https://www.softwebsolutions.com/power-bi-consulting-services/</v>
       </c>
       <c r="B37">
         <v>200</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://www.softwebsolutions.com/microsoft-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/azure-consulting-services/</v>
       </c>
       <c r="B38">
         <v>200</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://www.softwebsolutions.com/fabric-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/databricks-consulting-services/</v>
       </c>
       <c r="B39">
         <v>200</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://www.softwebsolutions.com/microsoft-copilot-studio-consulting/</v>
+        <v>https://www.softwebsolutions.com/azure-data-services/</v>
       </c>
       <c r="B40">
         <v>200</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://www.softwebsolutions.com/microsoft-365-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/azure-cloud-service/</v>
       </c>
       <c r="B41">
         <v>200</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://www.softwebsolutions.com/net-maui-development-services/</v>
+        <v>https://www.softwebsolutions.com/azure-ai-services/</v>
       </c>
       <c r="B42">
         <v>200</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://www.softwebsolutions.com/power-platform-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/aws-services/</v>
       </c>
       <c r="B43">
         <v>200</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://www.softwebsolutions.com/microsoft-power-apps-development/</v>
+        <v>https://www.softwebsolutions.com/aws-cloud-migration-services/</v>
       </c>
       <c r="B44">
         <v>200</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://www.softwebsolutions.com/power-automate-consulting/</v>
+        <v>https://www.softwebsolutions.com/aws-data-analytics-consulting/</v>
       </c>
       <c r="B45">
         <v>200</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>https://www.softwebsolutions.com/power-bi-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/aws-sagemaker-consulting-services/</v>
       </c>
       <c r="B46">
         <v>200</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>https://www.softwebsolutions.com/azure-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/salesforce-consulting-services/</v>
       </c>
       <c r="B47">
         <v>200</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>https://www.softwebsolutions.com/databricks-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/salesforce-development-services/</v>
       </c>
       <c r="B48">
         <v>200</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>https://www.softwebsolutions.com/azure-data-services/</v>
+        <v>https://www.softwebsolutions.com/salesforce-migration-services/</v>
       </c>
       <c r="B49">
         <v>200</v>
@@ -940,7 +940,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>https://www.softwebsolutions.com/azure-cloud-service/</v>
+        <v>https://www.softwebsolutions.com/salesforce-implementation-services/</v>
       </c>
       <c r="B50">
         <v>200</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>https://www.softwebsolutions.com/azure-ai-services/</v>
+        <v>https://www.softwebsolutions.com/salesforce-ai-consulting/</v>
       </c>
       <c r="B51">
         <v>200</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>https://www.softwebsolutions.com/aws-services/</v>
+        <v>https://www.softwebsolutions.com/about-softweb-solutions/</v>
       </c>
       <c r="B52">
         <v>200</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>https://www.softwebsolutions.com/aws-cloud-migration-services/</v>
+        <v>https://www.softwebsolutions.com/client-testimonial/</v>
       </c>
       <c r="B53">
         <v>200</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>https://www.softwebsolutions.com/aws-data-analytics-consulting/</v>
+        <v>https://www.softwebsolutions.com/resources/</v>
       </c>
       <c r="B54">
         <v>200</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>https://www.softwebsolutions.com/aws-sagemaker-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/supply-chain/</v>
       </c>
       <c r="B55">
         <v>200</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>https://www.softwebsolutions.com/salesforce-consulting-services/</v>
+        <v>https://www.softwebsolutions.com/manufacturing-industry/</v>
       </c>
       <c r="B56">
         <v>200</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>https://www.softwebsolutions.com/salesforce-development-services/</v>
+        <v>https://www.softwebsolutions.com/semiconductor/</v>
       </c>
       <c r="B57">
         <v>200</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>https://www.softwebsolutions.com/salesforce-migration-services/</v>
+        <v>https://www.softwebsolutions.com/telecom-industry/</v>
       </c>
       <c r="B58">
         <v>200</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>https://www.softwebsolutions.com/salesforce-implementation-services/</v>
+        <v>https://www.softwebsolutions.com/finance-industry/</v>
       </c>
       <c r="B59">
         <v>200</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>https://www.softwebsolutions.com/salesforce-ai-consulting/</v>
+        <v>https://www.softwebsolutions.com/portfolio/</v>
       </c>
       <c r="B60">
         <v>200</v>
